--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486298_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486298_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9353</v>
+        <v>5.6308</v>
       </c>
       <c r="E2" t="n">
-        <v>4.791</v>
+        <v>4.4558</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1442</v>
+        <v>1.175</v>
       </c>
       <c r="G2" t="n">
         <v>0.8983</v>
@@ -610,13 +610,13 @@
         <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6921</v>
+        <v>1.3877</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5141</v>
+        <v>1.1789</v>
       </c>
       <c r="U2" t="n">
-        <v>0.178</v>
+        <v>0.2088</v>
       </c>
       <c r="V2" t="n">
         <v>5.0849</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2087</v>
+        <v>4.8623</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6595</v>
+        <v>4.1692</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5492</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>3.2117</v>
@@ -688,13 +688,13 @@
         <v>2.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1047</v>
+        <v>0.7583</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.4074</v>
       </c>
       <c r="U3" t="n">
-        <v>0.207</v>
+        <v>0.3509</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1952</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.877</v>
+        <v>3.0909</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3123</v>
+        <v>0.8652</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5647</v>
+        <v>2.2256</v>
       </c>
       <c r="G4" t="n">
         <v>-0.3645</v>
@@ -766,13 +766,13 @@
         <v>2.3926</v>
       </c>
       <c r="S4" t="n">
-        <v>1.764</v>
+        <v>0.9779</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.5191</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7978</v>
+        <v>0.4587</v>
       </c>
       <c r="V4" t="n">
         <v>2.2599</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.565</v>
+        <v>3.0709</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2255</v>
+        <v>3.2998</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6605</v>
+        <v>-0.2289</v>
       </c>
       <c r="G5" t="n">
         <v>2.7004</v>
@@ -844,13 +844,13 @@
         <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0053</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8784</v>
+        <v>0.1959</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1269</v>
+        <v>0.3046</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5649999999999999</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4737</v>
+        <v>1.8822</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4893</v>
+        <v>0.7128</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9845</v>
+        <v>1.1694</v>
       </c>
       <c r="G6" t="n">
         <v>0.2444</v>
@@ -922,13 +922,13 @@
         <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3802</v>
+        <v>0.0282</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.274</v>
+        <v>-0.0505</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1062</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>0.7395</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1565</v>
+        <v>-0.2297</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0542</v>
+        <v>0.0575</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1022</v>
+        <v>-0.2872</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5812</v>
@@ -1000,13 +1000,13 @@
         <v>0.2175</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2072</v>
+        <v>0.134</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2055</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4127</v>
+        <v>0.2277</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BRIMAH</t>
+          <t>J. VAULET</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4789</v>
+        <v>-1.2486</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3704</v>
+        <v>-0.1377</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1086</v>
+        <v>-1.111</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.4961</v>
+        <v>-0.9335</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1375</v>
+        <v>1.0858</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3587</v>
+        <v>-2.0192</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6784</v>
+        <v>0.9823</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8696</v>
+        <v>1.5361</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1912</v>
+        <v>-0.5538</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8178</v>
+        <v>-1.9158</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2679</v>
+        <v>-0.4504</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5499</v>
+        <v>-1.4654</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0875</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3201</v>
+        <v>0.3374</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.822</v>
+        <v>-0.0324</v>
       </c>
       <c r="U8" t="n">
-        <v>1.1421</v>
+        <v>0.3698</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. VAULET</t>
+          <t>O. SILVERIO GRULLON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9183</v>
+        <v>-1.4926</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6532</v>
+        <v>-1.5198</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2651</v>
+        <v>0.0272</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9335</v>
+        <v>0.1327</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0858</v>
+        <v>-1.5542</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0192</v>
+        <v>1.687</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9823</v>
+        <v>1.568</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5361</v>
+        <v>-1.4354</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5538</v>
+        <v>3.0034</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9158</v>
+        <v>-1.4353</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4504</v>
+        <v>-0.1188</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4654</v>
+        <v>-1.3164</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6525</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R9" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3323</v>
+        <v>0.3545</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.548</v>
+        <v>-0.0204</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2157</v>
+        <v>0.3749</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. SILVERIO GRULLON</t>
+          <t>A. BRIMAH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9396</v>
+        <v>-1.6801</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9668</v>
+        <v>-0.0784</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0272</v>
+        <v>-1.6017</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1327</v>
+        <v>-2.4961</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5542</v>
+        <v>-1.1375</v>
       </c>
       <c r="I10" t="n">
-        <v>1.687</v>
+        <v>-1.3587</v>
       </c>
       <c r="J10" t="n">
-        <v>1.568</v>
+        <v>-0.6784</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.4354</v>
+        <v>-0.8696</v>
       </c>
       <c r="L10" t="n">
-        <v>3.0034</v>
+        <v>0.1912</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4353</v>
+        <v>-1.8178</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1188</v>
+        <v>-0.2679</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3164</v>
+        <v>-1.5499</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.1751</v>
+        <v>1.0875</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0925</v>
+        <v>0.119</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4675</v>
+        <v>-0.5299</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3749</v>
+        <v>0.6489</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1952</v>
+        <v>-0.3904</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8924</v>
+        <v>-4.0966</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2947</v>
+        <v>-3.4064</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5977</v>
+        <v>-0.6902</v>
       </c>
       <c r="G11" t="n">
         <v>-4.2537</v>
@@ -1312,13 +1312,13 @@
         <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7964</v>
+        <v>0.5921</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4026</v>
+        <v>0.2908</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3938</v>
+        <v>0.3013</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9275</v>
+        <v>-5.6491</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.26</v>
+        <v>-5.1973</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6675</v>
+        <v>-0.4518</v>
       </c>
       <c r="G12" t="n">
         <v>-3.2685</v>
@@ -1390,13 +1390,13 @@
         <v>2.1751</v>
       </c>
       <c r="S12" t="n">
-        <v>1.646</v>
+        <v>0.9244</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5057</v>
+        <v>0.5684</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1402</v>
+        <v>0.356</v>
       </c>
       <c r="V12" t="n">
         <v>-1.13</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.746499999999997</v>
+        <v>4.140400000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.878300000000003</v>
+        <v>3.220699999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8682000000000003</v>
+        <v>0.9194</v>
       </c>
       <c r="G13" t="n">
         <v>-4.710000000000001</v>
@@ -1468,16 +1468,16 @@
         <v>14.1378</v>
       </c>
       <c r="S13" t="n">
-        <v>5.7202</v>
+        <v>6.114</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0909</v>
+        <v>2.4336</v>
       </c>
       <c r="U13" t="n">
-        <v>3.6291</v>
+        <v>3.680299999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>5.9989</v>
+        <v>5.998900000000001</v>
       </c>
       <c r="W13" t="n">
         <v>10.1904</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3051</v>
+        <v>4.3622</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0052</v>
+        <v>2.8876</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2999</v>
+        <v>1.4746</v>
       </c>
       <c r="G14" t="n">
         <v>3.1267</v>
@@ -1546,13 +1546,13 @@
         <v>2.6101</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1784</v>
+        <v>0.2355</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1633</v>
+        <v>0.0457</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0151</v>
+        <v>0.1899</v>
       </c>
       <c r="V14" t="n">
         <v>0.5649999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1436</v>
+        <v>3.3119</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5501</v>
+        <v>3.6618</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4065</v>
+        <v>-0.3499</v>
       </c>
       <c r="G15" t="n">
         <v>0.743</v>
@@ -1624,13 +1624,13 @@
         <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5772</v>
+        <v>-0.4089</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4554</v>
+        <v>-0.3437</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1217</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>1.8902</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1573</v>
+        <v>2.9576</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6359</v>
+        <v>1.1947</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5214</v>
+        <v>1.7629</v>
       </c>
       <c r="G16" t="n">
         <v>2.1865</v>
@@ -1702,13 +1702,13 @@
         <v>2.3926</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5294</v>
+        <v>-0.7291</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3014</v>
+        <v>-0.7426</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.228</v>
+        <v>0.0135</v>
       </c>
       <c r="V16" t="n">
         <v>0.1952</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2583</v>
+        <v>0.4009</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1048</v>
+        <v>0.2165</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1536</v>
+        <v>0.1844</v>
       </c>
       <c r="G17" t="n">
         <v>0.2258</v>
@@ -1780,13 +1780,13 @@
         <v>0.2175</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1849</v>
+        <v>-0.0424</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2055</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0205</v>
+        <v>0.0514</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7763</v>
+        <v>-0.5785</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5229</v>
+        <v>-0.7464</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2534</v>
+        <v>0.1679</v>
       </c>
       <c r="G18" t="n">
         <v>1.5404</v>
@@ -1858,13 +1858,13 @@
         <v>2.6101</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5343</v>
+        <v>-0.3365</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3268</v>
+        <v>-0.5504</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2074</v>
+        <v>0.2139</v>
       </c>
       <c r="V18" t="n">
         <v>-1.13</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0495</v>
+        <v>-0.7386</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6261</v>
+        <v>-0.4026</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4234</v>
+        <v>-0.336</v>
       </c>
       <c r="G19" t="n">
         <v>0.1254</v>
@@ -1936,13 +1936,13 @@
         <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2826</v>
+        <v>0.0282</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.399</v>
+        <v>-0.1754</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1163</v>
+        <v>0.2037</v>
       </c>
       <c r="V19" t="n">
         <v>0.1952</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5828</v>
+        <v>-1.5622</v>
       </c>
       <c r="E20" t="n">
         <v>-1.6052</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0224</v>
+        <v>0.043</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7169</v>
@@ -2014,13 +2014,13 @@
         <v>2.6101</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1285</v>
+        <v>-0.1078</v>
       </c>
       <c r="T20" t="n">
         <v>-0.6128</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4844</v>
+        <v>0.505</v>
       </c>
       <c r="V20" t="n">
         <v>-2.2599</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. DE SOUSA ANJO BRITO</t>
+          <t>L. WESTERMANN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2452</v>
+        <v>-1.8356</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5701</v>
+        <v>-0.9141</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6751</v>
+        <v>-0.9216</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.7642</v>
+        <v>0.2894</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.882</v>
+        <v>-1.2286</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.8822</v>
+        <v>1.518</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2294</v>
+        <v>0.7166</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5991</v>
+        <v>-2.2867</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6303</v>
+        <v>3.0034</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5348</v>
+        <v>-0.4272</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2829</v>
+        <v>1.0582</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2519</v>
+        <v>-1.4854</v>
       </c>
       <c r="P21" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
-        <v>1.305</v>
+        <v>2.1751</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9813</v>
+        <v>-0.9526</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.536</v>
+        <v>-0.5432</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4454</v>
+        <v>-0.4095</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1952</v>
+        <v>-2.2599</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. WESTERMANN</t>
+          <t>D. DE SOUSA ANJO BRITO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2891</v>
+        <v>-2.0102</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2493</v>
+        <v>-1.4583</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0398</v>
+        <v>-0.5518</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2894</v>
+        <v>-2.7642</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2286</v>
+        <v>-0.882</v>
       </c>
       <c r="I22" t="n">
-        <v>1.518</v>
+        <v>-1.8822</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7166</v>
+        <v>-1.2294</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.2867</v>
+        <v>-0.5991</v>
       </c>
       <c r="L22" t="n">
-        <v>3.0034</v>
+        <v>-0.6303</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4272</v>
+        <v>-1.5348</v>
       </c>
       <c r="N22" t="n">
-        <v>1.0582</v>
+        <v>-0.2829</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4854</v>
+        <v>-1.2519</v>
       </c>
       <c r="P22" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1751</v>
+        <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4061</v>
+        <v>-0.7463</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8784</v>
+        <v>-0.4242</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5276999999999999</v>
+        <v>-0.3221</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.2599</v>
+        <v>0.1952</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6132</v>
+        <v>-2.6826</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.7311</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1056</v>
+        <v>-1.9515</v>
       </c>
       <c r="G23" t="n">
         <v>0.3095</v>
@@ -2248,13 +2248,13 @@
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4452</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1971</v>
+        <v>-0.0264</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6423</v>
+        <v>-0.4882</v>
       </c>
       <c r="V23" t="n">
         <v>-2.2599</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0547</v>
+        <v>-3.8813</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0829</v>
+        <v>-2.9711</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9718</v>
+        <v>-0.9102</v>
       </c>
       <c r="G24" t="n">
         <v>-0.3557</v>
@@ -2326,13 +2326,13 @@
         <v>0.435</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8289</v>
+        <v>-0.6555</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.274</v>
+        <v>-0.1622</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-0.4933</v>
       </c>
       <c r="V24" t="n">
         <v>-1.13</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.746500000000001</v>
+        <v>-2.256400000000002</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.8680999999999988</v>
+        <v>-0.868199999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.8783</v>
+        <v>-1.3882</v>
       </c>
       <c r="G25" t="n">
-        <v>4.709899999999999</v>
+        <v>4.7099</v>
       </c>
       <c r="H25" t="n">
         <v>5.232100000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5220999999999998</v>
+        <v>-0.5221000000000005</v>
       </c>
       <c r="J25" t="n">
         <v>12.7072</v>
@@ -2404,13 +2404,13 @@
         <v>17.4005</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.72</v>
+        <v>-4.23</v>
       </c>
       <c r="T25" t="n">
         <v>-3.6289</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.0911</v>
+        <v>-0.6009</v>
       </c>
       <c r="V25" t="n">
         <v>-5.9989</v>
